--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BA6239-631C-4453-B4A4-4E762374E871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8367AB8-312C-48F6-8E19-A13634C45705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -880,14 +880,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
   <dimension ref="A2:Q28"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
-    <col min="20" max="37" width="12.5625" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.125" style="4"/>
+    <col min="1" max="19" width="15.640625" style="4" customWidth="1"/>
+    <col min="20" max="37" width="12.5703125" style="4" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -940,7 +940,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -993,7 +993,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1122,7 +1122,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1150,13 +1150,13 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
@@ -1172,13 +1172,13 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
@@ -1191,13 +1191,13 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1206,13 +1206,13 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1221,13 +1221,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1236,13 +1236,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1251,13 +1251,13 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1266,7 +1266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1281,7 +1281,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1296,7 +1296,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1311,7 +1311,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1326,7 +1326,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1341,7 +1341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1356,7 +1356,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1371,7 +1371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1383,7 +1383,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1395,7 +1395,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1407,20 +1407,20 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="E25" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="E26" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="E28" s="1"/>
     </row>
   </sheetData>
